--- a/새서울철도-강남구-보고서.xlsx
+++ b/새서울철도-강남구-보고서.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\05 내 문서 모음\01. 업무관련 문서양식\017 지하안전점검(지하안전법) 관련\■ 연도별 지하안전점검(육안점검) 결과보고서\2026년 지하안전점검 보고서\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93EB5A72-E6D2-4917-AC23-8ED5DDF05D66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B604A600-6D74-448A-A411-DECDE7DDAEA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="785" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="641" uniqueCount="202">
   <si>
     <t>시행년도</t>
   </si>
@@ -288,12 +288,6 @@
     <t>26-강남구-01</t>
   </si>
   <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
     <t>신사동501</t>
   </si>
   <si>
@@ -373,9 +367,6 @@
   </si>
   <si>
     <t>26-강남구-10</t>
-  </si>
-  <si>
-    <t>1</t>
   </si>
   <si>
     <t>논현동143</t>
@@ -879,16 +870,16 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1244,7 +1235,7 @@
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C2" t="s">
         <v>3</v>
@@ -1343,23 +1334,23 @@
       <c r="I5" t="s">
         <v>28</v>
       </c>
-      <c r="J5" t="s">
-        <v>83</v>
-      </c>
-      <c r="K5" t="s">
-        <v>82</v>
-      </c>
-      <c r="L5" t="s">
-        <v>83</v>
-      </c>
-      <c r="M5" t="s">
-        <v>83</v>
-      </c>
-      <c r="N5" t="s">
-        <v>83</v>
-      </c>
-      <c r="O5" t="s">
-        <v>82</v>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>3</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>3</v>
       </c>
       <c r="P5" t="s">
         <v>29</v>
@@ -1368,13 +1359,13 @@
         <v>28</v>
       </c>
       <c r="R5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="S5" t="s">
         <v>30</v>
       </c>
       <c r="T5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="U5" t="s">
         <v>30</v>
@@ -1391,7 +1382,7 @@
         <v>24</v>
       </c>
       <c r="D6" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E6" t="s">
         <v>26</v>
@@ -1408,23 +1399,23 @@
       <c r="I6" t="s">
         <v>28</v>
       </c>
-      <c r="J6" t="s">
-        <v>83</v>
-      </c>
-      <c r="K6" t="s">
-        <v>82</v>
-      </c>
-      <c r="L6" t="s">
-        <v>83</v>
-      </c>
-      <c r="M6" t="s">
-        <v>83</v>
-      </c>
-      <c r="N6" t="s">
-        <v>83</v>
-      </c>
-      <c r="O6" t="s">
-        <v>82</v>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>3</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <v>3</v>
       </c>
       <c r="P6" t="s">
         <v>29</v>
@@ -1433,13 +1424,13 @@
         <v>28</v>
       </c>
       <c r="R6" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="S6" t="s">
         <v>30</v>
       </c>
       <c r="T6" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="U6" t="s">
         <v>30</v>
@@ -1456,7 +1447,7 @@
         <v>24</v>
       </c>
       <c r="D7" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E7" t="s">
         <v>26</v>
@@ -1473,23 +1464,23 @@
       <c r="I7" t="s">
         <v>28</v>
       </c>
-      <c r="J7" t="s">
-        <v>83</v>
-      </c>
-      <c r="K7" t="s">
-        <v>82</v>
-      </c>
-      <c r="L7" t="s">
-        <v>83</v>
-      </c>
-      <c r="M7" t="s">
-        <v>83</v>
-      </c>
-      <c r="N7" t="s">
-        <v>83</v>
-      </c>
-      <c r="O7" t="s">
-        <v>82</v>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>3</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>3</v>
       </c>
       <c r="P7" t="s">
         <v>29</v>
@@ -1498,13 +1489,13 @@
         <v>28</v>
       </c>
       <c r="R7" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="S7" t="s">
         <v>30</v>
       </c>
       <c r="T7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="U7" t="s">
         <v>30</v>
@@ -1521,7 +1512,7 @@
         <v>24</v>
       </c>
       <c r="D8" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E8" t="s">
         <v>26</v>
@@ -1538,23 +1529,23 @@
       <c r="I8" t="s">
         <v>28</v>
       </c>
-      <c r="J8" t="s">
-        <v>83</v>
-      </c>
-      <c r="K8" t="s">
-        <v>82</v>
-      </c>
-      <c r="L8" t="s">
-        <v>83</v>
-      </c>
-      <c r="M8" t="s">
-        <v>83</v>
-      </c>
-      <c r="N8" t="s">
-        <v>83</v>
-      </c>
-      <c r="O8" t="s">
-        <v>82</v>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>3</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <v>3</v>
       </c>
       <c r="P8" t="s">
         <v>29</v>
@@ -1563,13 +1554,13 @@
         <v>28</v>
       </c>
       <c r="R8" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="S8" t="s">
         <v>30</v>
       </c>
       <c r="T8" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="U8" t="s">
         <v>30</v>
@@ -1586,7 +1577,7 @@
         <v>24</v>
       </c>
       <c r="D9" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E9" t="s">
         <v>26</v>
@@ -1603,23 +1594,23 @@
       <c r="I9" t="s">
         <v>28</v>
       </c>
-      <c r="J9" t="s">
-        <v>83</v>
-      </c>
-      <c r="K9" t="s">
-        <v>82</v>
-      </c>
-      <c r="L9" t="s">
-        <v>83</v>
-      </c>
-      <c r="M9" t="s">
-        <v>83</v>
-      </c>
-      <c r="N9" t="s">
-        <v>83</v>
-      </c>
-      <c r="O9" t="s">
-        <v>82</v>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>3</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9">
+        <v>3</v>
       </c>
       <c r="P9" t="s">
         <v>29</v>
@@ -1628,13 +1619,13 @@
         <v>28</v>
       </c>
       <c r="R9" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="S9" t="s">
         <v>30</v>
       </c>
       <c r="T9" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="U9" t="s">
         <v>30</v>
@@ -1651,7 +1642,7 @@
         <v>24</v>
       </c>
       <c r="D10" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E10" t="s">
         <v>26</v>
@@ -1668,23 +1659,23 @@
       <c r="I10" t="s">
         <v>28</v>
       </c>
-      <c r="J10" t="s">
-        <v>83</v>
-      </c>
-      <c r="K10" t="s">
-        <v>82</v>
-      </c>
-      <c r="L10" t="s">
-        <v>83</v>
-      </c>
-      <c r="M10" t="s">
-        <v>83</v>
-      </c>
-      <c r="N10" t="s">
-        <v>83</v>
-      </c>
-      <c r="O10" t="s">
-        <v>82</v>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>3</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10">
+        <v>3</v>
       </c>
       <c r="P10" t="s">
         <v>29</v>
@@ -1693,13 +1684,13 @@
         <v>28</v>
       </c>
       <c r="R10" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="S10" t="s">
         <v>30</v>
       </c>
       <c r="T10" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="U10" t="s">
         <v>30</v>
@@ -1716,7 +1707,7 @@
         <v>24</v>
       </c>
       <c r="D11" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E11" t="s">
         <v>26</v>
@@ -1733,23 +1724,23 @@
       <c r="I11" t="s">
         <v>28</v>
       </c>
-      <c r="J11" t="s">
-        <v>83</v>
-      </c>
-      <c r="K11" t="s">
-        <v>82</v>
-      </c>
-      <c r="L11" t="s">
-        <v>83</v>
-      </c>
-      <c r="M11" t="s">
-        <v>83</v>
-      </c>
-      <c r="N11" t="s">
-        <v>83</v>
-      </c>
-      <c r="O11" t="s">
-        <v>82</v>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>3</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11">
+        <v>3</v>
       </c>
       <c r="P11" t="s">
         <v>29</v>
@@ -1758,13 +1749,13 @@
         <v>28</v>
       </c>
       <c r="R11" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="S11" t="s">
         <v>30</v>
       </c>
       <c r="T11" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="U11" t="s">
         <v>30</v>
@@ -1781,7 +1772,7 @@
         <v>24</v>
       </c>
       <c r="D12" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E12" t="s">
         <v>26</v>
@@ -1798,23 +1789,23 @@
       <c r="I12" t="s">
         <v>28</v>
       </c>
-      <c r="J12" t="s">
-        <v>83</v>
-      </c>
-      <c r="K12" t="s">
-        <v>82</v>
-      </c>
-      <c r="L12" t="s">
-        <v>83</v>
-      </c>
-      <c r="M12" t="s">
-        <v>83</v>
-      </c>
-      <c r="N12" t="s">
-        <v>83</v>
-      </c>
-      <c r="O12" t="s">
-        <v>82</v>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>3</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12">
+        <v>3</v>
       </c>
       <c r="P12" t="s">
         <v>29</v>
@@ -1823,13 +1814,13 @@
         <v>28</v>
       </c>
       <c r="R12" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="S12" t="s">
         <v>30</v>
       </c>
       <c r="T12" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="U12" t="s">
         <v>30</v>
@@ -1846,7 +1837,7 @@
         <v>24</v>
       </c>
       <c r="D13" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E13" t="s">
         <v>26</v>
@@ -1863,23 +1854,23 @@
       <c r="I13" t="s">
         <v>28</v>
       </c>
-      <c r="J13" t="s">
-        <v>83</v>
-      </c>
-      <c r="K13" t="s">
-        <v>82</v>
-      </c>
-      <c r="L13" t="s">
-        <v>83</v>
-      </c>
-      <c r="M13" t="s">
-        <v>83</v>
-      </c>
-      <c r="N13" t="s">
-        <v>83</v>
-      </c>
-      <c r="O13" t="s">
-        <v>82</v>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>3</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13">
+        <v>3</v>
       </c>
       <c r="P13" t="s">
         <v>29</v>
@@ -1888,13 +1879,13 @@
         <v>28</v>
       </c>
       <c r="R13" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="S13" t="s">
         <v>30</v>
       </c>
       <c r="T13" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="U13" t="s">
         <v>30</v>
@@ -1911,7 +1902,7 @@
         <v>24</v>
       </c>
       <c r="D14" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E14" t="s">
         <v>26</v>
@@ -1928,23 +1919,23 @@
       <c r="I14" t="s">
         <v>28</v>
       </c>
-      <c r="J14" t="s">
-        <v>83</v>
-      </c>
-      <c r="K14" t="s">
-        <v>111</v>
-      </c>
-      <c r="L14" t="s">
-        <v>83</v>
-      </c>
-      <c r="M14" t="s">
-        <v>83</v>
-      </c>
-      <c r="N14" t="s">
-        <v>83</v>
-      </c>
-      <c r="O14" t="s">
-        <v>111</v>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>1</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14">
+        <v>1</v>
       </c>
       <c r="P14" t="s">
         <v>29</v>
@@ -1953,13 +1944,13 @@
         <v>28</v>
       </c>
       <c r="R14" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="S14" t="s">
         <v>30</v>
       </c>
       <c r="T14" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="U14" t="s">
         <v>30</v>
@@ -1976,7 +1967,7 @@
         <v>24</v>
       </c>
       <c r="D15" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E15" t="s">
         <v>26</v>
@@ -1993,23 +1984,23 @@
       <c r="I15" t="s">
         <v>28</v>
       </c>
-      <c r="J15" t="s">
-        <v>83</v>
-      </c>
-      <c r="K15" t="s">
-        <v>82</v>
-      </c>
-      <c r="L15" t="s">
-        <v>83</v>
-      </c>
-      <c r="M15" t="s">
-        <v>83</v>
-      </c>
-      <c r="N15" t="s">
-        <v>83</v>
-      </c>
-      <c r="O15" t="s">
-        <v>82</v>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>3</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15">
+        <v>3</v>
       </c>
       <c r="P15" t="s">
         <v>29</v>
@@ -2018,13 +2009,13 @@
         <v>28</v>
       </c>
       <c r="R15" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="S15" t="s">
         <v>30</v>
       </c>
       <c r="T15" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="U15" t="s">
         <v>30</v>
@@ -2041,7 +2032,7 @@
         <v>24</v>
       </c>
       <c r="D16" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E16" t="s">
         <v>26</v>
@@ -2058,23 +2049,23 @@
       <c r="I16" t="s">
         <v>28</v>
       </c>
-      <c r="J16" t="s">
-        <v>83</v>
-      </c>
-      <c r="K16" t="s">
-        <v>82</v>
-      </c>
-      <c r="L16" t="s">
-        <v>83</v>
-      </c>
-      <c r="M16" t="s">
-        <v>83</v>
-      </c>
-      <c r="N16" t="s">
-        <v>83</v>
-      </c>
-      <c r="O16" t="s">
-        <v>82</v>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>3</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16">
+        <v>0</v>
+      </c>
+      <c r="O16">
+        <v>3</v>
       </c>
       <c r="P16" t="s">
         <v>29</v>
@@ -2083,13 +2074,13 @@
         <v>28</v>
       </c>
       <c r="R16" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="S16" t="s">
         <v>30</v>
       </c>
       <c r="T16" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="U16" t="s">
         <v>30</v>
@@ -2106,7 +2097,7 @@
         <v>24</v>
       </c>
       <c r="D17" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E17" t="s">
         <v>26</v>
@@ -2123,23 +2114,23 @@
       <c r="I17" t="s">
         <v>28</v>
       </c>
-      <c r="J17" t="s">
-        <v>83</v>
-      </c>
-      <c r="K17" t="s">
-        <v>82</v>
-      </c>
-      <c r="L17" t="s">
-        <v>83</v>
-      </c>
-      <c r="M17" t="s">
-        <v>83</v>
-      </c>
-      <c r="N17" t="s">
-        <v>83</v>
-      </c>
-      <c r="O17" t="s">
-        <v>82</v>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>3</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17">
+        <v>0</v>
+      </c>
+      <c r="O17">
+        <v>3</v>
       </c>
       <c r="P17" t="s">
         <v>29</v>
@@ -2148,13 +2139,13 @@
         <v>42</v>
       </c>
       <c r="R17" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="S17" t="s">
         <v>30</v>
       </c>
       <c r="T17" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="U17" t="s">
         <v>30</v>
@@ -2171,7 +2162,7 @@
         <v>24</v>
       </c>
       <c r="D18" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E18" t="s">
         <v>26</v>
@@ -2188,23 +2179,23 @@
       <c r="I18" t="s">
         <v>28</v>
       </c>
-      <c r="J18" t="s">
-        <v>83</v>
-      </c>
-      <c r="K18" t="s">
-        <v>82</v>
-      </c>
-      <c r="L18" t="s">
-        <v>83</v>
-      </c>
-      <c r="M18" t="s">
-        <v>83</v>
-      </c>
-      <c r="N18" t="s">
-        <v>83</v>
-      </c>
-      <c r="O18" t="s">
-        <v>82</v>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>3</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18">
+        <v>0</v>
+      </c>
+      <c r="O18">
+        <v>3</v>
       </c>
       <c r="P18" t="s">
         <v>29</v>
@@ -2213,13 +2204,13 @@
         <v>28</v>
       </c>
       <c r="R18" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="S18" t="s">
         <v>30</v>
       </c>
       <c r="T18" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="U18" t="s">
         <v>30</v>
@@ -2236,7 +2227,7 @@
         <v>24</v>
       </c>
       <c r="D19" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E19" t="s">
         <v>26</v>
@@ -2253,23 +2244,23 @@
       <c r="I19" t="s">
         <v>28</v>
       </c>
-      <c r="J19" t="s">
-        <v>83</v>
-      </c>
-      <c r="K19" t="s">
-        <v>82</v>
-      </c>
-      <c r="L19" t="s">
-        <v>83</v>
-      </c>
-      <c r="M19" t="s">
-        <v>83</v>
-      </c>
-      <c r="N19" t="s">
-        <v>83</v>
-      </c>
-      <c r="O19" t="s">
-        <v>82</v>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>3</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19">
+        <v>0</v>
+      </c>
+      <c r="O19">
+        <v>3</v>
       </c>
       <c r="P19" t="s">
         <v>29</v>
@@ -2278,13 +2269,13 @@
         <v>28</v>
       </c>
       <c r="R19" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="S19" t="s">
         <v>30</v>
       </c>
       <c r="T19" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="U19" t="s">
         <v>30</v>
@@ -2301,7 +2292,7 @@
         <v>24</v>
       </c>
       <c r="D20" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="E20" t="s">
         <v>26</v>
@@ -2318,23 +2309,23 @@
       <c r="I20" t="s">
         <v>28</v>
       </c>
-      <c r="J20" t="s">
-        <v>83</v>
-      </c>
-      <c r="K20" t="s">
-        <v>82</v>
-      </c>
-      <c r="L20" t="s">
-        <v>83</v>
-      </c>
-      <c r="M20" t="s">
-        <v>83</v>
-      </c>
-      <c r="N20" t="s">
-        <v>83</v>
-      </c>
-      <c r="O20" t="s">
-        <v>82</v>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>3</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="N20">
+        <v>0</v>
+      </c>
+      <c r="O20">
+        <v>3</v>
       </c>
       <c r="P20" t="s">
         <v>29</v>
@@ -2343,13 +2334,13 @@
         <v>28</v>
       </c>
       <c r="R20" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="S20" t="s">
         <v>30</v>
       </c>
       <c r="T20" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="U20" t="s">
         <v>30</v>
@@ -2366,7 +2357,7 @@
         <v>24</v>
       </c>
       <c r="D21" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="E21" t="s">
         <v>26</v>
@@ -2383,23 +2374,23 @@
       <c r="I21" t="s">
         <v>28</v>
       </c>
-      <c r="J21" t="s">
-        <v>83</v>
-      </c>
-      <c r="K21" t="s">
-        <v>111</v>
-      </c>
-      <c r="L21" t="s">
-        <v>83</v>
-      </c>
-      <c r="M21" t="s">
-        <v>83</v>
-      </c>
-      <c r="N21" t="s">
-        <v>83</v>
-      </c>
-      <c r="O21" t="s">
-        <v>111</v>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>1</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21">
+        <v>0</v>
+      </c>
+      <c r="O21">
+        <v>1</v>
       </c>
       <c r="P21" t="s">
         <v>29</v>
@@ -2408,13 +2399,13 @@
         <v>28</v>
       </c>
       <c r="R21" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="S21" t="s">
         <v>30</v>
       </c>
       <c r="T21" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="U21" t="s">
         <v>30</v>
@@ -2431,7 +2422,7 @@
         <v>24</v>
       </c>
       <c r="D22" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="E22" t="s">
         <v>26</v>
@@ -2448,23 +2439,23 @@
       <c r="I22" t="s">
         <v>28</v>
       </c>
-      <c r="J22" t="s">
-        <v>83</v>
-      </c>
-      <c r="K22" t="s">
-        <v>82</v>
-      </c>
-      <c r="L22" t="s">
-        <v>83</v>
-      </c>
-      <c r="M22" t="s">
-        <v>83</v>
-      </c>
-      <c r="N22" t="s">
-        <v>83</v>
-      </c>
-      <c r="O22" t="s">
-        <v>82</v>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>3</v>
+      </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+      <c r="N22">
+        <v>0</v>
+      </c>
+      <c r="O22">
+        <v>3</v>
       </c>
       <c r="P22" t="s">
         <v>29</v>
@@ -2473,13 +2464,13 @@
         <v>28</v>
       </c>
       <c r="R22" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="S22" t="s">
         <v>30</v>
       </c>
       <c r="T22" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="U22" t="s">
         <v>30</v>
@@ -2496,7 +2487,7 @@
         <v>24</v>
       </c>
       <c r="D23" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="E23" t="s">
         <v>26</v>
@@ -2513,23 +2504,23 @@
       <c r="I23" t="s">
         <v>28</v>
       </c>
-      <c r="J23" t="s">
-        <v>83</v>
-      </c>
-      <c r="K23" t="s">
-        <v>82</v>
-      </c>
-      <c r="L23" t="s">
-        <v>83</v>
-      </c>
-      <c r="M23" t="s">
-        <v>83</v>
-      </c>
-      <c r="N23" t="s">
-        <v>83</v>
-      </c>
-      <c r="O23" t="s">
-        <v>82</v>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>3</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
+      </c>
+      <c r="N23">
+        <v>0</v>
+      </c>
+      <c r="O23">
+        <v>3</v>
       </c>
       <c r="P23" t="s">
         <v>29</v>
@@ -2538,13 +2529,13 @@
         <v>28</v>
       </c>
       <c r="R23" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="S23" t="s">
         <v>30</v>
       </c>
       <c r="T23" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="U23" t="s">
         <v>30</v>
@@ -2561,7 +2552,7 @@
         <v>24</v>
       </c>
       <c r="D24" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="E24" t="s">
         <v>26</v>
@@ -2578,23 +2569,23 @@
       <c r="I24" t="s">
         <v>28</v>
       </c>
-      <c r="J24" t="s">
-        <v>83</v>
-      </c>
-      <c r="K24" t="s">
-        <v>82</v>
-      </c>
-      <c r="L24" t="s">
-        <v>83</v>
-      </c>
-      <c r="M24" t="s">
-        <v>83</v>
-      </c>
-      <c r="N24" t="s">
-        <v>83</v>
-      </c>
-      <c r="O24" t="s">
-        <v>82</v>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <v>3</v>
+      </c>
+      <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24">
+        <v>0</v>
+      </c>
+      <c r="N24">
+        <v>0</v>
+      </c>
+      <c r="O24">
+        <v>3</v>
       </c>
       <c r="P24" t="s">
         <v>29</v>
@@ -2603,13 +2594,13 @@
         <v>28</v>
       </c>
       <c r="R24" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="S24" t="s">
         <v>30</v>
       </c>
       <c r="T24" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="U24" t="s">
         <v>30</v>
@@ -2626,7 +2617,7 @@
         <v>24</v>
       </c>
       <c r="D25" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="E25" t="s">
         <v>26</v>
@@ -2643,23 +2634,23 @@
       <c r="I25" t="s">
         <v>28</v>
       </c>
-      <c r="J25" t="s">
-        <v>83</v>
-      </c>
-      <c r="K25" t="s">
-        <v>82</v>
-      </c>
-      <c r="L25" t="s">
-        <v>83</v>
-      </c>
-      <c r="M25" t="s">
-        <v>83</v>
-      </c>
-      <c r="N25" t="s">
-        <v>83</v>
-      </c>
-      <c r="O25" t="s">
-        <v>82</v>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>3</v>
+      </c>
+      <c r="L25">
+        <v>0</v>
+      </c>
+      <c r="M25">
+        <v>0</v>
+      </c>
+      <c r="N25">
+        <v>0</v>
+      </c>
+      <c r="O25">
+        <v>3</v>
       </c>
       <c r="P25" t="s">
         <v>29</v>
@@ -2668,13 +2659,13 @@
         <v>28</v>
       </c>
       <c r="R25" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="S25" t="s">
         <v>30</v>
       </c>
       <c r="T25" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="U25" t="s">
         <v>30</v>
@@ -2691,7 +2682,7 @@
         <v>24</v>
       </c>
       <c r="D26" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="E26" t="s">
         <v>26</v>
@@ -2708,23 +2699,23 @@
       <c r="I26" t="s">
         <v>28</v>
       </c>
-      <c r="J26" t="s">
-        <v>83</v>
-      </c>
-      <c r="K26" t="s">
-        <v>82</v>
-      </c>
-      <c r="L26" t="s">
-        <v>83</v>
-      </c>
-      <c r="M26" t="s">
-        <v>83</v>
-      </c>
-      <c r="N26" t="s">
-        <v>83</v>
-      </c>
-      <c r="O26" t="s">
-        <v>82</v>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <v>3</v>
+      </c>
+      <c r="L26">
+        <v>0</v>
+      </c>
+      <c r="M26">
+        <v>0</v>
+      </c>
+      <c r="N26">
+        <v>0</v>
+      </c>
+      <c r="O26">
+        <v>3</v>
       </c>
       <c r="P26" t="s">
         <v>29</v>
@@ -2733,13 +2724,13 @@
         <v>28</v>
       </c>
       <c r="R26" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="S26" t="s">
         <v>30</v>
       </c>
       <c r="T26" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="U26" t="s">
         <v>30</v>
@@ -2756,7 +2747,7 @@
         <v>24</v>
       </c>
       <c r="D27" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E27" t="s">
         <v>26</v>
@@ -2773,23 +2764,23 @@
       <c r="I27" t="s">
         <v>28</v>
       </c>
-      <c r="J27" t="s">
-        <v>83</v>
-      </c>
-      <c r="K27" t="s">
-        <v>82</v>
-      </c>
-      <c r="L27" t="s">
-        <v>83</v>
-      </c>
-      <c r="M27" t="s">
-        <v>83</v>
-      </c>
-      <c r="N27" t="s">
-        <v>83</v>
-      </c>
-      <c r="O27" t="s">
-        <v>82</v>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <v>3</v>
+      </c>
+      <c r="L27">
+        <v>0</v>
+      </c>
+      <c r="M27">
+        <v>0</v>
+      </c>
+      <c r="N27">
+        <v>0</v>
+      </c>
+      <c r="O27">
+        <v>3</v>
       </c>
       <c r="P27" t="s">
         <v>29</v>
@@ -2798,13 +2789,13 @@
         <v>28</v>
       </c>
       <c r="R27" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="S27" t="s">
         <v>30</v>
       </c>
       <c r="T27" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="U27" t="s">
         <v>30</v>
@@ -2821,7 +2812,7 @@
         <v>24</v>
       </c>
       <c r="D28" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E28" t="s">
         <v>26</v>
@@ -2838,23 +2829,23 @@
       <c r="I28" t="s">
         <v>28</v>
       </c>
-      <c r="J28" t="s">
-        <v>83</v>
-      </c>
-      <c r="K28" t="s">
-        <v>82</v>
-      </c>
-      <c r="L28" t="s">
-        <v>83</v>
-      </c>
-      <c r="M28" t="s">
-        <v>83</v>
-      </c>
-      <c r="N28" t="s">
-        <v>83</v>
-      </c>
-      <c r="O28" t="s">
-        <v>82</v>
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28">
+        <v>3</v>
+      </c>
+      <c r="L28">
+        <v>0</v>
+      </c>
+      <c r="M28">
+        <v>0</v>
+      </c>
+      <c r="N28">
+        <v>0</v>
+      </c>
+      <c r="O28">
+        <v>3</v>
       </c>
       <c r="P28" t="s">
         <v>29</v>
@@ -2863,13 +2854,13 @@
         <v>28</v>
       </c>
       <c r="R28" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="S28" t="s">
         <v>30</v>
       </c>
       <c r="T28" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="U28" t="s">
         <v>30</v>
@@ -2886,7 +2877,7 @@
         <v>24</v>
       </c>
       <c r="D29" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="E29" t="s">
         <v>26</v>
@@ -2925,13 +2916,13 @@
         <v>29</v>
       </c>
       <c r="R29" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="S29" t="s">
         <v>30</v>
       </c>
       <c r="T29" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="U29" t="s">
         <v>30</v>
@@ -2948,7 +2939,7 @@
         <v>24</v>
       </c>
       <c r="D30" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="E30" t="s">
         <v>26</v>
@@ -2990,13 +2981,13 @@
         <v>42</v>
       </c>
       <c r="R30" t="s">
+        <v>174</v>
+      </c>
+      <c r="S30" t="s">
+        <v>30</v>
+      </c>
+      <c r="T30" t="s">
         <v>177</v>
-      </c>
-      <c r="S30" t="s">
-        <v>30</v>
-      </c>
-      <c r="T30" t="s">
-        <v>180</v>
       </c>
       <c r="U30" t="s">
         <v>30</v>
@@ -3058,7 +3049,7 @@
         <v>30</v>
       </c>
       <c r="T31" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="U31" t="s">
         <v>30</v>
@@ -3114,13 +3105,13 @@
         <v>29</v>
       </c>
       <c r="R32" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="S32" t="s">
         <v>30</v>
       </c>
       <c r="T32" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="U32" t="s">
         <v>30</v>
@@ -3182,7 +3173,7 @@
         <v>30</v>
       </c>
       <c r="T33" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="U33" t="s">
         <v>30</v>
@@ -3244,7 +3235,7 @@
         <v>30</v>
       </c>
       <c r="T34" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="U34" t="s">
         <v>30</v>
@@ -3306,7 +3297,7 @@
         <v>30</v>
       </c>
       <c r="T35" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="U35" t="s">
         <v>30</v>
@@ -3368,7 +3359,7 @@
         <v>30</v>
       </c>
       <c r="T36" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="U36" t="s">
         <v>30</v>
@@ -3433,7 +3424,7 @@
         <v>30</v>
       </c>
       <c r="T37" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="U37" t="s">
         <v>30</v>
@@ -3495,7 +3486,7 @@
         <v>30</v>
       </c>
       <c r="T38" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="U38" t="s">
         <v>30</v>
@@ -3557,7 +3548,7 @@
         <v>30</v>
       </c>
       <c r="T39" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="U39" t="s">
         <v>30</v>
@@ -3619,7 +3610,7 @@
         <v>30</v>
       </c>
       <c r="T40" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="U40" t="s">
         <v>30</v>
@@ -3681,7 +3672,7 @@
         <v>30</v>
       </c>
       <c r="T41" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="U41" t="s">
         <v>30</v>
@@ -3746,7 +3737,7 @@
         <v>30</v>
       </c>
       <c r="T42" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="U42" t="s">
         <v>30</v>
@@ -3808,7 +3799,7 @@
         <v>30</v>
       </c>
       <c r="T43" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="U43" t="s">
         <v>30</v>
@@ -3870,7 +3861,7 @@
         <v>30</v>
       </c>
       <c r="T44" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="U44" t="s">
         <v>30</v>
@@ -3932,7 +3923,7 @@
         <v>30</v>
       </c>
       <c r="T45" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="U45" t="s">
         <v>30</v>
@@ -3997,7 +3988,7 @@
         <v>30</v>
       </c>
       <c r="T46" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="U46" t="s">
         <v>30</v>
@@ -4059,7 +4050,7 @@
         <v>30</v>
       </c>
       <c r="T47" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="U47" t="s">
         <v>30</v>
@@ -4121,7 +4112,7 @@
         <v>30</v>
       </c>
       <c r="T48" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="U48" t="s">
         <v>30</v>
@@ -4186,7 +4177,7 @@
         <v>30</v>
       </c>
       <c r="T49" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="U49" t="s">
         <v>30</v>
@@ -4251,7 +4242,7 @@
         <v>30</v>
       </c>
       <c r="T50" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="U50" t="s">
         <v>30</v>
@@ -4313,7 +4304,7 @@
         <v>30</v>
       </c>
       <c r="T51" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="U51" t="s">
         <v>30</v>
@@ -4375,7 +4366,7 @@
         <v>30</v>
       </c>
       <c r="T52" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="U52" t="s">
         <v>30</v>
@@ -4437,7 +4428,7 @@
         <v>30</v>
       </c>
       <c r="T53" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="U53" t="s">
         <v>30</v>
@@ -4496,7 +4487,7 @@
         <v>78</v>
       </c>
       <c r="T54" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.3">
@@ -4552,14 +4543,14 @@
         <v>80</v>
       </c>
       <c r="T55" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="E1:U1 B3:U4 E2:U2 C7:G28 C5:G5 I5:U5 I6:U28 C6:G6" numberStoredAsText="1"/>
+    <ignoredError sqref="E1:U1 B3:U4 E2:U2 C7:G28 C5:G5 I5 I6:I28 C6:G6 P5:U5 P6:U28" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -4585,7 +4576,7 @@
   <sheetData>
     <row r="2" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="2"/>
@@ -4622,66 +4613,66 @@
       <c r="P3" s="2"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A4" s="14" t="s">
+      <c r="A4" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="B4" s="11"/>
+      <c r="C4" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="D4" s="11"/>
+      <c r="E4" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="F4" s="11"/>
+      <c r="G4" s="9" t="s">
         <v>157</v>
       </c>
-      <c r="B4" s="13"/>
-      <c r="C4" s="14" t="s">
+      <c r="H4" s="10"/>
+      <c r="I4" s="11"/>
+      <c r="J4" s="9" t="s">
         <v>158</v>
       </c>
-      <c r="D4" s="13"/>
-      <c r="E4" s="14" t="s">
+      <c r="K4" s="10"/>
+      <c r="L4" s="11"/>
+      <c r="M4" s="9" t="s">
         <v>159</v>
       </c>
-      <c r="F4" s="13"/>
-      <c r="G4" s="14" t="s">
-        <v>160</v>
-      </c>
-      <c r="H4" s="12"/>
-      <c r="I4" s="13"/>
-      <c r="J4" s="14" t="s">
-        <v>161</v>
-      </c>
-      <c r="K4" s="12"/>
-      <c r="L4" s="13"/>
-      <c r="M4" s="14" t="s">
-        <v>162</v>
-      </c>
-      <c r="N4" s="12"/>
-      <c r="O4" s="12"/>
-      <c r="P4" s="13"/>
+      <c r="N4" s="10"/>
+      <c r="O4" s="10"/>
+      <c r="P4" s="11"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A5" s="14" t="s">
-        <v>173</v>
-      </c>
-      <c r="B5" s="13"/>
-      <c r="C5" s="14" t="str">
+      <c r="A5" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="B5" s="11"/>
+      <c r="C5" s="9" t="str">
         <f>RawData!C2</f>
         <v>강남구</v>
       </c>
-      <c r="D5" s="13"/>
-      <c r="E5" s="14" t="s">
-        <v>163</v>
-      </c>
-      <c r="F5" s="13"/>
-      <c r="G5" s="14" t="s">
-        <v>164</v>
-      </c>
-      <c r="H5" s="12"/>
-      <c r="I5" s="13"/>
-      <c r="J5" s="14" t="str">
+      <c r="D5" s="11"/>
+      <c r="E5" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="F5" s="11"/>
+      <c r="G5" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="H5" s="10"/>
+      <c r="I5" s="11"/>
+      <c r="J5" s="9" t="str">
         <f>RawData!B2</f>
         <v>새서울철도㈜</v>
       </c>
-      <c r="K5" s="12"/>
-      <c r="L5" s="13"/>
-      <c r="M5" s="14" t="s">
-        <v>165</v>
-      </c>
-      <c r="N5" s="12"/>
-      <c r="O5" s="12"/>
-      <c r="P5" s="13"/>
+      <c r="K5" s="10"/>
+      <c r="L5" s="11"/>
+      <c r="M5" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="N5" s="10"/>
+      <c r="O5" s="10"/>
+      <c r="P5" s="11"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A6" s="2"/>
@@ -4702,43 +4693,43 @@
       <c r="P6" s="2"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A7" s="9" t="s">
+      <c r="A7" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="11" t="s">
-        <v>166</v>
-      </c>
-      <c r="E7" s="12"/>
-      <c r="F7" s="12"/>
-      <c r="G7" s="12"/>
-      <c r="H7" s="13"/>
-      <c r="I7" s="11" t="s">
-        <v>167</v>
-      </c>
-      <c r="J7" s="12"/>
-      <c r="K7" s="12"/>
-      <c r="L7" s="12"/>
-      <c r="M7" s="13"/>
-      <c r="N7" s="9" t="s">
+      <c r="D7" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="E7" s="10"/>
+      <c r="F7" s="10"/>
+      <c r="G7" s="10"/>
+      <c r="H7" s="11"/>
+      <c r="I7" s="14" t="s">
+        <v>164</v>
+      </c>
+      <c r="J7" s="10"/>
+      <c r="K7" s="10"/>
+      <c r="L7" s="10"/>
+      <c r="M7" s="11"/>
+      <c r="N7" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="O7" s="9" t="s">
+      <c r="O7" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="P7" s="9" t="s">
-        <v>168</v>
+      <c r="P7" s="12" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="8" spans="1:19" s="5" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="10"/>
-      <c r="B8" s="10"/>
-      <c r="C8" s="10"/>
+      <c r="A8" s="13"/>
+      <c r="B8" s="13"/>
+      <c r="C8" s="13"/>
       <c r="D8" s="4" t="s">
         <v>7</v>
       </c>
@@ -4752,10 +4743,10 @@
         <v>10</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="J8" s="4" t="s">
         <v>8</v>
@@ -4764,14 +4755,14 @@
         <v>9</v>
       </c>
       <c r="L8" s="4" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="M8" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="N8" s="10"/>
-      <c r="O8" s="10"/>
-      <c r="P8" s="10"/>
+      <c r="N8" s="13"/>
+      <c r="O8" s="13"/>
+      <c r="P8" s="13"/>
       <c r="Q8" s="3"/>
       <c r="R8" s="3"/>
       <c r="S8" s="3"/>
@@ -6362,6 +6353,14 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="O7:O8"/>
+    <mergeCell ref="P7:P8"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="D7:H7"/>
+    <mergeCell ref="I7:M7"/>
+    <mergeCell ref="N7:N8"/>
     <mergeCell ref="M5:P5"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="C4:D4"/>
@@ -6374,14 +6373,6 @@
     <mergeCell ref="E5:F5"/>
     <mergeCell ref="G5:I5"/>
     <mergeCell ref="J5:L5"/>
-    <mergeCell ref="O7:O8"/>
-    <mergeCell ref="P7:P8"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="D7:H7"/>
-    <mergeCell ref="I7:M7"/>
-    <mergeCell ref="N7:N8"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
